--- a/2022 data/excel_outputs/183_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/183_boothwise_data.xlsx
@@ -14,180 +14,291 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="390">
   <si>
     <t>AC 183 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
+  </si>
+  <si>
+    <t>Unnamed: 25</t>
+  </si>
+  <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
     <t>POLLING STATION NAME</t>
   </si>
   <si>
-    <t>####0##0 #######</t>
-  </si>
-  <si>
-    <t>####0##0 ########### kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0 ########### kkss sN-2</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##### ##### kkss sN -1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##### ##### kkss sN -2</t>
-  </si>
-  <si>
-    <t>####0##0 ########</t>
-  </si>
-  <si>
-    <t>####0##0 ####### kkss sN0-1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### kkss sN0-2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### kkss sN-2</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ### kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ### kkss sN-2</t>
-  </si>
-  <si>
-    <t>####0##0 ##########</t>
-  </si>
-  <si>
-    <t>####0##0 ###########</t>
-  </si>
-  <si>
-    <t>##### ##0 ######</t>
-  </si>
-  <si>
-    <t>####0##0 #####</t>
-  </si>
-  <si>
-    <t>####0##0 ###### kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### kkss sN-2</t>
-  </si>
-  <si>
-    <t>####0##0 ##### kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0 ##### kkss sN-2</t>
-  </si>
-  <si>
-    <t>####0##0 ######</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ######</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ###</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ##### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #####</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ######</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ####### ###### kkss sN-1</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ####### ###### kkss sN-2</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #####</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ####### kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ####### kkss sN-2</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ##### ####### kkss sN-1</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ##### ####### kkss sN-2</t>
-  </si>
-  <si>
-    <t>####0##0 ## ##### ##### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ########## ####</t>
-  </si>
-  <si>
-    <t>####0##0 #### #### ########## ####</t>
-  </si>
-  <si>
-    <t>##0##0##0 ###### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ########### ###### ;###### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ####</t>
-  </si>
-  <si>
-    <t>####0##0 #### ##### kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0 #### ##### kkss sN-2</t>
-  </si>
-  <si>
-    <t>####0##0 #### ######</t>
-  </si>
-  <si>
-    <t>###### ### #####</t>
-  </si>
-  <si>
-    <t>####0##0 ####</t>
-  </si>
-  <si>
-    <t>####0##0 ######## kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0 ######## kkss sN-2</t>
-  </si>
-  <si>
-    <t>####0##0 #########</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### kkss sN-2</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ########## ##### kkss sN-1</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ########## #####kkss sN-2</t>
-  </si>
-  <si>
-    <t>####0##0 #### kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0 #### kkss sN-2</t>
+    <t>A0 V0 BAHE RAYA</t>
+  </si>
+  <si>
+    <t>A0 V0 NARE PARU</t>
+  </si>
+  <si>
+    <t>A0 V0 RAYAPARU T PA HAVEL</t>
+  </si>
+  <si>
+    <t>A0 V0 CH JAP U RU</t>
+  </si>
+  <si>
+    <t>A0 V0 SALEMAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 KHAL LAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 KURAUL DAMA</t>
+  </si>
+  <si>
+    <t>A0 V0 SE DARU AMAU</t>
+  </si>
+  <si>
+    <t>A0 V0 MANASAKH U MAU</t>
+  </si>
+  <si>
+    <t>A0 V0 RADHABALAMAPARU</t>
+  </si>
+  <si>
+    <t>!KASAN V0 BADERAVA</t>
+  </si>
+  <si>
+    <t>A0 V0 SAHAMADA</t>
+  </si>
+  <si>
+    <t>A0 V0 TE$LAYANI</t>
+  </si>
+  <si>
+    <t>A0 V0 S TAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 SARU SANA</t>
+  </si>
+  <si>
+    <t>A0 V0 BHARASANA</t>
+  </si>
+  <si>
+    <t>A0 V0 K DHARAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 D NAGAMJ</t>
+  </si>
+  <si>
+    <t>A0 V0 SAMRAY LAKHAMI</t>
+  </si>
+  <si>
+    <t>A0 V0 SHOBHAVAPARU PAKHARAUL</t>
+  </si>
+  <si>
+    <t>A0 V0 PAKHARAUL</t>
+  </si>
+  <si>
+    <t>A0 V0 CHAMDAPARU LAK U</t>
+  </si>
+  <si>
+    <t>A0 V0 $MAJA,PARU UPH, SARU JAPARU SAI/BASI</t>
+  </si>
+  <si>
+    <t>A0 V0 K0YANAPARU B1 TI</t>
+  </si>
+  <si>
+    <t>A0 V0 NARAHARAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 DHAMA,PARU</t>
+  </si>
+  <si>
+    <t>A0 V0 TARAPARU BAMSI</t>
+  </si>
+  <si>
+    <t>A0 V0 RASAL U PARU DHARAMVA</t>
+  </si>
+  <si>
+    <t>JU0HA0 2KUL RASAL U PARU DHARAMVA</t>
+  </si>
+  <si>
+    <t>A0 V0 NEVADA PATAT</t>
+  </si>
+  <si>
+    <t>A0 V0 DHIRANAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 VASHUNADASAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAPARU BARARA</t>
+  </si>
+  <si>
+    <t>A0 V0 BARARA BAJ U UG ,</t>
+  </si>
+  <si>
+    <t>A0 V0 UDHANAPARU</t>
+  </si>
+  <si>
+    <t>JU0HA0 2KUL BARARA BAJ U UG ,</t>
+  </si>
+  <si>
+    <t>A0 V0 BAN PARU VA BARARA BAJ U UG ,</t>
+  </si>
+  <si>
+    <t>A0 V0 GO V DAPARU MADHAV</t>
+  </si>
+  <si>
+    <t>A0 V0 PARU E BABA GO V DAPARU MADHAV</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 CH4HAR IJAYAYAK</t>
+  </si>
+  <si>
+    <t>A0 V0 NARE PUR CH4HAR (CH4HAR IJAYAYAK)</t>
+  </si>
+  <si>
+    <t>A0 V0 DHAMA,PARU KAIL</t>
+  </si>
+  <si>
+    <t>A0 V0 !KATUL</t>
+  </si>
+  <si>
+    <t>A0 V0 SARU JAPARU BANAPAR</t>
+  </si>
+  <si>
+    <t>A0 V0 GAURA KHASAPAR</t>
+  </si>
+  <si>
+    <t>A0 V0 THAL U RAI</t>
+  </si>
+  <si>
+    <t>A0 V0 PARU E RATHAURAN</t>
+  </si>
+  <si>
+    <t>PAMCHAYAT BHAVAN THAL U RAI</t>
+  </si>
+  <si>
+    <t>A0 V0 GHARU</t>
+  </si>
+  <si>
+    <t>A0 V0 ME0THAV U A</t>
+  </si>
+  <si>
+    <t>A0 V0 I2MAILAMAU</t>
+  </si>
+  <si>
+    <t>A0 V0 CHAL U</t>
+  </si>
+  <si>
+    <t>A0 V0 GARU GAJ U PARU</t>
+  </si>
+  <si>
+    <t>A0 V0 MELAKHA SAHAB</t>
+  </si>
+  <si>
+    <t>JU0HA0 2KUL S0 U TANAPARU JANAUL</t>
+  </si>
+  <si>
+    <t>DY0 J0 L|SHRADYASHRCH JDYASDY</t>
+  </si>
+  <si>
+    <t>A0 V0 SAMI</t>
+  </si>
+  <si>
+    <t>A0 V0 &lt;B NAVA</t>
+  </si>
+  <si>
+    <t>A0 V0 PARU E HASAUPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 GAURA HARADO</t>
+  </si>
+  <si>
+    <t>JU0HA0 2KUL GAURA HARADO</t>
+  </si>
+  <si>
+    <t>A0 V0 PARU E BAKHAT</t>
+  </si>
+  <si>
+    <t>A0 V0 BADA PARU VA</t>
+  </si>
+  <si>
+    <t>A0 V0 SAT U THA HARADO</t>
+  </si>
+  <si>
+    <t>A0 V0 GADAGAMJ</t>
+  </si>
+  <si>
+    <t>PAMCHAYAT BHAVAN !KASHOR BALAMAPARU</t>
   </si>
   <si>
     <t>praa0 vi0 hsuupur kkss sN-1</t>
@@ -199,502 +310,568 @@
     <t>praa0vi0 gauraa hrdo</t>
   </si>
   <si>
-    <t>##0##0 ##### #### #### kkss sN-1</t>
-  </si>
-  <si>
-    <t>##0##0 ##### #### #### kkss sN-2</t>
+    <t>JU0HA0 2KUL JALALAPARU DHAI</t>
   </si>
   <si>
     <t>praa0vi0 puure bkht</t>
   </si>
   <si>
-    <t>####0##0 bddaa' purvaa</t>
-  </si>
-  <si>
-    <t>###### ### ###### #######</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ####### ## kkss sN-1</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ####### ## kkss sN-2</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ####### ## kkss sN-3</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ####### ## kkss sN-4</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ###</t>
-  </si>
-  <si>
-    <t>####0##0 #### (###### ###)</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ###### ##### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #####</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ###### kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ###### kkss sN-2</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##########</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ####### kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ####### kkss sN-2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ### kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ### kkss sN-2</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##### kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##### kkss sN-2</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ######</t>
-  </si>
-  <si>
-    <t>####0##0 #### ######## kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0 #### ######## kkss sN-2</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ######## #### kkss sN-1</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ######## #### kkss sN-2</t>
-  </si>
-  <si>
-    <t>####0##0####### ####</t>
-  </si>
-  <si>
-    <t>####0##0 #### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ##########</t>
-  </si>
-  <si>
-    <t>####0##0 #### ########</t>
-  </si>
-  <si>
-    <t>####0##0####### #####</t>
-  </si>
-  <si>
-    <t>####0##0####### ###</t>
-  </si>
-  <si>
-    <t>##0##0###### ####</t>
-  </si>
-  <si>
-    <t>#### ####### ,########</t>
-  </si>
-  <si>
-    <t>##0##0##0########</t>
-  </si>
-  <si>
-    <t>##0##0##########</t>
-  </si>
-  <si>
-    <t>####0##0####### #### #####</t>
-  </si>
-  <si>
-    <t>####0##0#######</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ########</t>
-  </si>
-  <si>
-    <t>####0##0### #### ##01</t>
-  </si>
-  <si>
-    <t>####0##0### #### ##02</t>
-  </si>
-  <si>
-    <t>####0##0######</t>
-  </si>
-  <si>
-    <t>####0##0####</t>
-  </si>
-  <si>
-    <t>####0##0##### #### ##01</t>
-  </si>
-  <si>
-    <t>####0##0##### #### ##02</t>
-  </si>
-  <si>
-    <t>#0####0##0#####</t>
-  </si>
-  <si>
-    <t>####0##0##########</t>
-  </si>
-  <si>
-    <t>####0##0############### ##01</t>
-  </si>
-  <si>
-    <t>####0##0############### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0####### #### #######</t>
-  </si>
-  <si>
-    <t>####0##0######## #### ##01</t>
-  </si>
-  <si>
-    <t>####0##0######## #### ##02</t>
-  </si>
-  <si>
-    <t>####0##0###### ####### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0###### ####### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0###### ####### #### ##03</t>
-  </si>
-  <si>
-    <t>####0##0###### #######</t>
-  </si>
-  <si>
-    <t>####0##0#### ### ####</t>
-  </si>
-  <si>
-    <t>####0##0###### ########</t>
-  </si>
-  <si>
-    <t>####0##0########### ######</t>
-  </si>
-  <si>
-    <t>####0##0######### ##### #### ##01</t>
-  </si>
-  <si>
-    <t>####0##0######### ##### #### ##02</t>
-  </si>
-  <si>
-    <t>####0##0#####</t>
-  </si>
-  <si>
-    <t>####0##0#########</t>
-  </si>
-  <si>
-    <t>##0 ##0 ######</t>
-  </si>
-  <si>
-    <t>####0##0########## #### ##01</t>
-  </si>
-  <si>
-    <t>####0##0########## #### ##02</t>
-  </si>
-  <si>
-    <t>##0##0 ###### #### ##01</t>
-  </si>
-  <si>
-    <t>##0##0 ###### #### ##02</t>
-  </si>
-  <si>
-    <t>##0## ######</t>
-  </si>
-  <si>
-    <t>####0##0######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0####;#####</t>
-  </si>
-  <si>
-    <t>####0##0####### kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0###### #### ##01</t>
-  </si>
-  <si>
-    <t>####0##0###### #### ##02</t>
-  </si>
-  <si>
-    <t>##### ####0 ###### ##### kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0###### kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0##### kkss sN-1</t>
-  </si>
-  <si>
-    <t>##0##0######### #### ##0 1</t>
-  </si>
-  <si>
-    <t>##0##0######### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0#### ##### #### ##01</t>
-  </si>
-  <si>
-    <t>####0##0#### ##### #### ##02</t>
-  </si>
-  <si>
-    <t>####0##0#### #### #### kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0#### ####### #0 #### kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0#### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0#### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0#### ##### kkss sN-1</t>
-  </si>
-  <si>
-    <t>##0## ########### ######## kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0####### #### ##01</t>
-  </si>
-  <si>
-    <t>####0##0####### #### ##02</t>
-  </si>
-  <si>
-    <t>####0##0######## ######### kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0########## kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0######## ### #### ##01</t>
-  </si>
-  <si>
-    <t>####0##0######## ### #### ##02</t>
-  </si>
-  <si>
-    <t>####0##0######## ### #### ##03</t>
-  </si>
-  <si>
-    <t>####0## ###### kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0#### #### #### ##01</t>
-  </si>
-  <si>
-    <t>####0##0#### #### #### ##02</t>
-  </si>
-  <si>
-    <t>####0##0##### ####### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0##### ####### #### ##0 2</t>
-  </si>
-  <si>
-    <t>##0##0 ##0##### ####### kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0#### #### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0#### #### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0#### #######;##### ####### kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0###### ;##### ####### #### ##01</t>
-  </si>
-  <si>
-    <t>####0##0###### ;##### ####### #### ##02</t>
-  </si>
-  <si>
-    <t>##0##0##0 ######### ##### kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0##### ###### kkss sN-1</t>
-  </si>
-  <si>
-    <t>##0##0##0 ##### kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0####### #### ##03</t>
-  </si>
-  <si>
-    <t>####0##0####### #### ##04</t>
-  </si>
-  <si>
-    <t>##0##0###### kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0########## ##01</t>
-  </si>
-  <si>
-    <t>####0##0########## ##02</t>
-  </si>
-  <si>
-    <t>####0##0########### ##01</t>
-  </si>
-  <si>
-    <t>####0##0########### ##02</t>
-  </si>
-  <si>
-    <t>####0##0########### ##03</t>
-  </si>
-  <si>
-    <t>##0##0########### ##01</t>
-  </si>
-  <si>
-    <t>##0##0########### ##02</t>
-  </si>
-  <si>
-    <t>####0##0###### #0 ####### #### ##01</t>
-  </si>
-  <si>
-    <t>####0##0###### #0 ####### #### ##02</t>
-  </si>
-  <si>
-    <t>####0##0############ #### ##01</t>
-  </si>
-  <si>
-    <t>####0##0############ #### ##02</t>
-  </si>
-  <si>
-    <t>####0##0####### ####### kkss sN-1</t>
-  </si>
-  <si>
-    <t>########, ########### kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0######## ##01</t>
-  </si>
-  <si>
-    <t>####0##0######## ##02</t>
-  </si>
-  <si>
-    <t>##0 ##0 ####0 #### #### ##01</t>
-  </si>
-  <si>
-    <t>##0##0 ######## ##02</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######## kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0####### ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0####### ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0####### ######## #### ##0 3</t>
-  </si>
-  <si>
-    <t>####0##0##### ####### kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0######### ###### kkss sN-1</t>
-  </si>
-  <si>
-    <t>##0 ##0 ####### ###;######### ##### #### ##01</t>
-  </si>
-  <si>
-    <t>##0 ##0 ####### ###;######### ##### #### ##0 2</t>
-  </si>
-  <si>
-    <t>##0##0##0 ######## ### ######01</t>
-  </si>
-  <si>
-    <t>##0##0##0 ######## ### ######02</t>
-  </si>
-  <si>
-    <t>####0##0#### #######, ############### ##01</t>
-  </si>
-  <si>
-    <t>####0##0#### #######, ############### ##02</t>
-  </si>
-  <si>
-    <t>####0##0######,####### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0###### ####### #### ##0 3</t>
-  </si>
-  <si>
-    <t>####0##0######### ### kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0## ####### kkss sN-1</t>
-  </si>
-  <si>
-    <t>####0##0########### #### ##01</t>
-  </si>
-  <si>
-    <t>####0##0########### #### ##02</t>
-  </si>
-  <si>
-    <t>##0##0########</t>
-  </si>
-  <si>
-    <t>####0##0######### ##01</t>
-  </si>
-  <si>
-    <t>####0##0######### ##02</t>
-  </si>
-  <si>
-    <t>####0##0###### ########## ##01</t>
-  </si>
-  <si>
-    <t>####0##0###### ########## ##02</t>
-  </si>
-  <si>
-    <t>##0 ##0 ###### ###### #### ##0 1</t>
-  </si>
-  <si>
-    <t>##0 ##0 ###### ###### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0########</t>
-  </si>
-  <si>
-    <t>####0##0######## ###### #### ##01</t>
-  </si>
-  <si>
-    <t>####0##0######## ###### #### ##02</t>
-  </si>
-  <si>
-    <t>####0##0######## ###### #### ##03</t>
-  </si>
-  <si>
-    <t>####0##0############ ##01</t>
-  </si>
-  <si>
-    <t>####0##0##### ### #### ##02</t>
-  </si>
-  <si>
-    <t>####0##0############ ##02</t>
-  </si>
-  <si>
-    <t>####0##0###########</t>
-  </si>
-  <si>
-    <t>####0##0##### ####</t>
-  </si>
-  <si>
-    <t>####0##0############# ##01</t>
-  </si>
-  <si>
-    <t>####0##0############# ##02</t>
-  </si>
-  <si>
-    <t>####0##0######## ####</t>
+    <t>A0 V0 GODA (CH4HAR VIK)</t>
+  </si>
+  <si>
+    <t>A0 V0 K=RATAPUR CH4HAR U.CPH, DE VAGANA</t>
+  </si>
+  <si>
+    <t>A0 V0 NARAYANAPARU B NA</t>
+  </si>
+  <si>
+    <t>A0 V0 RAYAPARU GAUR</t>
+  </si>
+  <si>
+    <t>A0 V0 PAYAGAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 CH DAI CH4HAR</t>
+  </si>
+  <si>
+    <t>A0 V0 CH4HAR ASHAN DAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 BHAGAVAMTAPARU CHAMD@NAHA</t>
+  </si>
+  <si>
+    <t>A0 V0 HAMIRAMAU</t>
+  </si>
+  <si>
+    <t>A0 V0 SARADARAGAMJ</t>
+  </si>
+  <si>
+    <t>A0 V0 DHAMADHAMA</t>
+  </si>
+  <si>
+    <t>A0 V0 DAUDAPARU GADAI</t>
+  </si>
+  <si>
+    <t>A0 V0 KURAUL BUDHAKAR</t>
+  </si>
+  <si>
+    <t>A0 V0 BAMSI RAHAYAK</t>
+  </si>
+  <si>
+    <t>A0 V0 MARU AI THAA</t>
+  </si>
+  <si>
+    <t>A0 V0 A/BARA MATHAI</t>
+  </si>
+  <si>
+    <t>A0 V0 T KAR AGACHIPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 JHARAHA</t>
+  </si>
+  <si>
+    <t>A0 V0 @CHACHAURA</t>
+  </si>
+  <si>
+    <t>JU0HA0 2KUL ALAVALAPARU MADHAU</t>
+  </si>
+  <si>
+    <t>A0 V0 BEH KHOR</t>
+  </si>
+  <si>
+    <t>PRA.VI.. BHANUVAMAU</t>
+  </si>
+  <si>
+    <t>PRA.VI.. JALALAPUR BEHI</t>
+  </si>
+  <si>
+    <t>PRA.VI.. GAURA LAKHAMI</t>
+  </si>
+  <si>
+    <t>PRA.VI.. TIKATHA MUSALLEPUR</t>
+  </si>
+  <si>
+    <t>PRA.VI.. SARAYASHRIBAKS</t>
+  </si>
+  <si>
+    <t>PRA.VI.. KEVALAPURABARETHA</t>
+  </si>
+  <si>
+    <t>PRA.VI.. DHARMADASAPUR</t>
+  </si>
+  <si>
+    <t>J.UHA.SANHU KUAM</t>
+  </si>
+  <si>
+    <t>PRA.VI. PURETIKARIYA,HARADITIKAR</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 BENIKAMA</t>
+  </si>
+  <si>
+    <t>JUA.DHARMADASAPUR</t>
+  </si>
+  <si>
+    <t>PRA.VI.. NAVABAGAMJ</t>
+  </si>
+  <si>
+    <t>PRA.VI.. SIDDHAUR</t>
+  </si>
+  <si>
+    <t>P.GHAR HEVATAHA NEVADHIYA</t>
+  </si>
+  <si>
+    <t>PRA.VI.. BHIKH</t>
+  </si>
+  <si>
+    <t>PRA.VI..BHIKH</t>
+  </si>
+  <si>
+    <t>PRA.VI.. JAMO.DI</t>
+  </si>
+  <si>
+    <t>PRA.VI.. UMARI</t>
+  </si>
+  <si>
+    <t>PRA.VI. U.DAVA</t>
+  </si>
+  <si>
+    <t>PRA.VI.. U.DAVA</t>
+  </si>
+  <si>
+    <t>PRA.VI.. BICHIYAVADI</t>
+  </si>
+  <si>
+    <t>PRA.VI.. SHERANDAJAPUR</t>
+  </si>
+  <si>
+    <t>PRA.VI.. DAULATAPUR</t>
+  </si>
+  <si>
+    <t>PRA.VI.. SHITALAPUR URPHASHAMKARAPUR</t>
+  </si>
+  <si>
+    <t>PRA.VI.. PURABAGA.CV</t>
+  </si>
+  <si>
+    <t>PRA.VI.. RAMAGADHATIKARIYA</t>
+  </si>
+  <si>
+    <t>PRA.VI.. RAMAGADH.TIKARIYA</t>
+  </si>
+  <si>
+    <t>PRA.VI.. ROJHAIYA BHIKHAMASHAH</t>
+  </si>
+  <si>
+    <t>PRA.VI. PURE JHAM SIMH</t>
+  </si>
+  <si>
+    <t>PRA.VI..ROJHAIYA GOKULAPUR</t>
+  </si>
+  <si>
+    <t>PRA.VI. IBRAHIM JADHAIYA</t>
+  </si>
+  <si>
+    <t>PRA.VI..KALYANAPUR SURAJARI</t>
+  </si>
+  <si>
+    <t>PRA.VI..DHOBAHA</t>
+  </si>
+  <si>
+    <t>PRA.VI..TIVARIPUR</t>
+  </si>
+  <si>
+    <t>PRA.VI.. TIVARIPUR</t>
+  </si>
+  <si>
+    <t>JUA.JIMGANA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 LAKSHMANAPUR</t>
+  </si>
+  <si>
+    <t>JUA.JAGATAPUR</t>
+  </si>
+  <si>
+    <t>PAM.GHAR JAGATAPUR</t>
+  </si>
+  <si>
+    <t>PRA.VI.. MANOHARAGAMJ</t>
+  </si>
+  <si>
+    <t>PRA.VI.. KUD (TAMGHAN)</t>
+  </si>
+  <si>
+    <t>PRA.VI.. BAIRIHAR</t>
+  </si>
+  <si>
+    <t>PRA.VI.. CHICHAILI</t>
+  </si>
+  <si>
+    <t>KANYA PRA.VI. CHICHAILI</t>
+  </si>
+  <si>
+    <t>PRA.VI.. KHAJURI</t>
+  </si>
+  <si>
+    <t>PRA.VI.. CHICHEMAU</t>
+  </si>
+  <si>
+    <t>PRA.VI.. HATHAKURI</t>
+  </si>
+  <si>
+    <t>PRA.VI.. KUSUMI</t>
+  </si>
+  <si>
+    <t>JUA. SUDAMAPUR</t>
+  </si>
+  <si>
+    <t>PRA.VI..PURE KAKORAN</t>
+  </si>
+  <si>
+    <t>PRA.VI..PURE SHAMKARABAKS</t>
+  </si>
+  <si>
+    <t>PRA.VI.. PURE SUBEDAR M0 DHUTA</t>
+  </si>
+  <si>
+    <t>PRA.VI..DHUTA</t>
+  </si>
+  <si>
+    <t>JUUA.DHUTA</t>
+  </si>
+  <si>
+    <t>PRA.VI. PURE NASIRAN</t>
+  </si>
+  <si>
+    <t>PAM.GHAR.MUTAVALLIPUR RANA SAHAB</t>
+  </si>
+  <si>
+    <t>PRA.VI..KAJIYANA</t>
+  </si>
+  <si>
+    <t>PRA.VI. MAKHADUMAPUR MUNIMABAD</t>
+  </si>
+  <si>
+    <t>PRA.VI. MANIHARASHARKI</t>
+  </si>
+  <si>
+    <t>PRA.VI..KISHANUDASAPUR</t>
+  </si>
+  <si>
+    <t>PRA.VI. KISHUNADASAPUR</t>
+  </si>
+  <si>
+    <t>PRA.VI. KAMOLI</t>
+  </si>
+  <si>
+    <t>PAMCHA. GHAR PURANAMAU</t>
+  </si>
+  <si>
+    <t>PRA.VI. SARAMY HARADO</t>
+  </si>
+  <si>
+    <t>PRA.VI..ITAURABUJURG</t>
+  </si>
+  <si>
+    <t>PRA0PA0 PURE BABA</t>
+  </si>
+  <si>
+    <t>PRA.VI. PURE BABA</t>
+  </si>
+  <si>
+    <t>PRA.VI. ITAURABUJURG</t>
+  </si>
+  <si>
+    <t>PRA.VI..PURE GURUDIN(ITAURA BUJURG)</t>
+  </si>
+  <si>
+    <t>PRA.VI. BAMSHAPUR(ITAURA BUJURG)</t>
+  </si>
+  <si>
+    <t>PRA0VI0 CHIPIYA</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 KHANAALAMAPUR SATAHARA</t>
+  </si>
+  <si>
+    <t>PRA.VI. AIHARIBUJARG</t>
+  </si>
+  <si>
+    <t>PRA.VI. MIRJAPUR AIHARI</t>
+  </si>
+  <si>
+    <t>PRA.VI. RAYAPUR</t>
+  </si>
+  <si>
+    <t>PRA.VI. DHAMOLI</t>
+  </si>
+  <si>
+    <t>PRA.VI. ROHANIYA</t>
+  </si>
+  <si>
+    <t>JUA.DHAURAHARA</t>
+  </si>
+  <si>
+    <t>PRA.VI. USARAINA</t>
+  </si>
+  <si>
+    <t>PRA.VI.RASULAPUR</t>
+  </si>
+  <si>
+    <t>PRA.VI. RASULAPUR</t>
+  </si>
+  <si>
+    <t>JU0HA0 SKUL RASULAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SAMASAPUR M0 RASULAPUR</t>
+  </si>
+  <si>
+    <t>PRA.VI. SARAYAKHITAYAR</t>
+  </si>
+  <si>
+    <t>PRA.VI. SALIMAPURABAHERAVAR</t>
+  </si>
+  <si>
+    <t>PRA.VI. MATARAMAPUR</t>
+  </si>
+  <si>
+    <t>PRA.VI. MAVARI</t>
+  </si>
+  <si>
+    <t>PRA.VI..MAVARI</t>
+  </si>
+  <si>
+    <t>PRA.VI. PARASIPUR</t>
+  </si>
+  <si>
+    <t>PRA.VI. SARAKAPUR</t>
+  </si>
+  <si>
+    <t>PRA.VI. KAMALAPUR</t>
+  </si>
+  <si>
+    <t>RAINABASERA .SAMASAPUR PATAUNA</t>
+  </si>
+  <si>
+    <t>PRA.VI. UMARAN</t>
+  </si>
+  <si>
+    <t>PRA.VI..UMARAN</t>
+  </si>
+  <si>
+    <t>JUA.UMARAN</t>
+  </si>
+  <si>
+    <t>PRA.VI. GAMGEHARAGULALAGAMJ</t>
+  </si>
+  <si>
+    <t>PRA.VI. DELAULI</t>
+  </si>
+  <si>
+    <t>PRA.VI..DELAULI</t>
+  </si>
+  <si>
+    <t>PRA.VI. CHATAUNAMARIYANI</t>
+  </si>
+  <si>
+    <t>PRA.VI. RAGHUNATHAPUR LABEDAVA</t>
+  </si>
+  <si>
+    <t>JUA.PAYAGAPUR NADAURA</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 KHALIKAPURAKALA.C</t>
+  </si>
+  <si>
+    <t>PRA.VI. NEVADA</t>
+  </si>
+  <si>
+    <t>PRA.VI. PURE KUMARIN,SEMARIRANAPUR</t>
+  </si>
+  <si>
+    <t>PRA.VI..MATARAULI,BABUGAMJ</t>
+  </si>
+  <si>
+    <t>PRA.VI. MATARAULI BABUGAMJ</t>
+  </si>
+  <si>
+    <t>PRA.VI. RAMACHANDRAPUR</t>
+  </si>
+  <si>
+    <t>PRA.VI. CH.DARARI</t>
+  </si>
+  <si>
+    <t>PRA.VI..RAMASAMDA</t>
+  </si>
+  <si>
+    <t>PAMCHAYAT GHAR DAULATAPUR</t>
+  </si>
+  <si>
+    <t>PRA.VI. SARABAHADA</t>
+  </si>
+  <si>
+    <t>PRA.VI. RISHVARADASAPUR</t>
+  </si>
+  <si>
+    <t>PRA.VI. .RISHVARADASAPUR</t>
+  </si>
+  <si>
+    <t>JU0HA0 SKUL JAMUNAPUR</t>
+  </si>
+  <si>
+    <t>PRA.VI. PACHAKHARA</t>
+  </si>
+  <si>
+    <t>PRA.VI. GOKANA</t>
+  </si>
+  <si>
+    <t>PRA.VI. KOTIYA CHITRA</t>
+  </si>
+  <si>
+    <t>JUA.KOTIYA CHITRA</t>
+  </si>
+  <si>
+    <t>JA.KOTIYA CHITRA</t>
+  </si>
+  <si>
+    <t>PRA.VI. SHAHAJADAPUR</t>
+  </si>
+  <si>
+    <t>PRA.VI. SAMVAPUR NEVADA</t>
+  </si>
+  <si>
+    <t>PRA.VI..SAMVAPUR NEVADA</t>
+  </si>
+  <si>
+    <t>PRA.VI.SAVAIYADHANI</t>
+  </si>
+  <si>
+    <t>PRA.VI..SAVAIYADHANI</t>
+  </si>
+  <si>
+    <t>PRA.VI..SAVAIYA HASAN</t>
+  </si>
+  <si>
+    <t>PRA.VI.SAVAIYA HASAN</t>
+  </si>
+  <si>
+    <t>PRA.VI. SARAYATULARAM</t>
+  </si>
+  <si>
+    <t>PRA.VI. HATAVA</t>
+  </si>
+  <si>
+    <t>PRA.VI. SAVAIYA MIRA</t>
+  </si>
+  <si>
+    <t>PRA.VI. KHOJANAPUR</t>
+  </si>
+  <si>
+    <t>PRA.VI..SAVAIYA RAJE</t>
+  </si>
+  <si>
+    <t>PRA.VI.MANIRAMAPUR</t>
+  </si>
+  <si>
+    <t>PRA.VI. GOPALAPUR UDHAVAN</t>
+  </si>
+  <si>
+    <t>PRA.VI. KHURRAMAPUR</t>
+  </si>
+  <si>
+    <t>PRA.VI. BAHERAVA</t>
+  </si>
+  <si>
+    <t>PRA.VI. BHUVALAPUR</t>
+  </si>
+  <si>
+    <t>PAM.BHAVAN MADARIPUR</t>
+  </si>
+  <si>
+    <t>PAM.GHARAMURARAMAU</t>
+  </si>
+  <si>
+    <t>PRA.VI. SARENI</t>
+  </si>
+  <si>
+    <t>PRA.VI..LALACHANDRAPUR EKACHANIYA</t>
+  </si>
+  <si>
+    <t>PRA.VI.GAMGASARI</t>
+  </si>
+  <si>
+    <t>PRA.VI..ITAILI</t>
+  </si>
+  <si>
+    <t>PRA.VI. ALI NAGAR ASAKARANAPUR</t>
+  </si>
+  <si>
+    <t>PRA.VI.AMIDAPUR B.DAGA.CV</t>
+  </si>
+  <si>
+    <t>PRA.VI. BEHARAMAU</t>
+  </si>
+  <si>
+    <t>PRA.VI. HAHIRAPUR</t>
+  </si>
+  <si>
+    <t>PRA.VI. SHUKARULLAPUR</t>
+  </si>
+  <si>
+    <t>PRA.VI. MADHAUPUR SULTAN</t>
+  </si>
+  <si>
+    <t>PRA.VI..AMAJAHANIYA</t>
+  </si>
+  <si>
+    <t>PRA.VI..SALIMAPUR BHAIROM</t>
+  </si>
+  <si>
+    <t>PRA.VI. PURAVARA</t>
+  </si>
+  <si>
+    <t>PRA.VI..SARAY SAMHIJAN</t>
+  </si>
+  <si>
+    <t>PRA.VI..MOKHARA</t>
+  </si>
+  <si>
+    <t>PRA.VI. BIKARI</t>
+  </si>
+  <si>
+    <t>PU.MA.NAP. U.NCHAHAR ENATIPISI0 ROD</t>
+  </si>
+  <si>
+    <t>PU.MA.NAP. U.NCHAHAR ENATIPIASI0 ROD</t>
+  </si>
+  <si>
+    <t>PRA0VI0 GADHI PIPARAHA U.NCHAHAR</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 NAM0PAM0 UMCHAHAR</t>
+  </si>
+  <si>
+    <t>DIEVI.U.NCHAHAR</t>
+  </si>
+  <si>
+    <t>PRA.VI..U.NCHAHAR</t>
+  </si>
+  <si>
+    <t>PRA.VI. U.NCHAHAR</t>
+  </si>
+  <si>
+    <t>JUA.U.NCHAHAR(THANE KE PAS)</t>
+  </si>
+  <si>
+    <t>PRA0VI0 UMCHAHAR THANE KE PAS</t>
+  </si>
+  <si>
+    <t>PRA.VI. GAMGAULI</t>
+  </si>
+  <si>
+    <t>PRA.VI. HORAISA</t>
   </si>
   <si>
     <t>praa0vi0 puure gautmn,mdaariipur</t>
@@ -703,58 +880,85 @@
     <t>praa0vi0 bhvaaniidiinpur, muraarmuu</t>
   </si>
   <si>
-    <t>####0##0########## #######</t>
-  </si>
-  <si>
-    <t>####0##0####### ########</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### ##01</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0############</t>
-  </si>
-  <si>
-    <t>####0##0####### #######</t>
-  </si>
-  <si>
-    <t>####0##0####### ######## ##01</t>
-  </si>
-  <si>
-    <t>####0##0####### ######## ##02</t>
-  </si>
-  <si>
-    <t>####0##0#### ######### ##01</t>
-  </si>
-  <si>
-    <t>####0##0 #### ##### #### ##02</t>
-  </si>
-  <si>
-    <t>####0##0#### #### ##01</t>
-  </si>
-  <si>
-    <t>####0##0#### #### ##02</t>
-  </si>
-  <si>
-    <t>####0##0######## ##03</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ####### ######## ### #### ##01</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ####### ######## ### #### ##02</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0 ####### ######## ### #### ##0 3</t>
-  </si>
-  <si>
-    <t>######0 #### ##0 ###0 #######</t>
-  </si>
-  <si>
-    <t>####0##0#### ###### #######</t>
+    <t>PRA.VI. PURELOK MISAH KHARAULI</t>
+  </si>
+  <si>
+    <t>PAM.GHAR,KHARAULI</t>
+  </si>
+  <si>
+    <t>PRA.VI. KALYANI</t>
+  </si>
+  <si>
+    <t>PRA.VI..JABBARIPUR</t>
+  </si>
+  <si>
+    <t>JUA.KAMDARAVA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 GAMGAGADH</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PRAHALADAPUR</t>
+  </si>
+  <si>
+    <t>PRA.VI. PURE LODIPUR,KAMDARAVA</t>
+  </si>
+  <si>
+    <t>PRA.VI. KADARAMVA</t>
+  </si>
+  <si>
+    <t>PRA.VI..KADARAMVA</t>
+  </si>
+  <si>
+    <t>PRA.VI..PAT़TI RAHASAKAITHAVAL</t>
+  </si>
+  <si>
+    <t>PRA.VI. PATTI RAHAS KAITHAVAL</t>
+  </si>
+  <si>
+    <t>PRA.VI..PATTI RAHAS KAITHAVAL</t>
+  </si>
+  <si>
+    <t>P.GHAR PATTI RAHAS KAITHAVAL</t>
+  </si>
+  <si>
+    <t>DAVAKARA BHAVAN (PAM.GHAR KAIMPAS ME PATTIRAHASAKAITHAVALAM)</t>
+  </si>
+  <si>
+    <t>PRA.VI..ARAKHA</t>
+  </si>
+  <si>
+    <t>PRA.VI. ARAKHA</t>
+  </si>
+  <si>
+    <t>J.VI.ARAKHA</t>
+  </si>
+  <si>
+    <t>PRA.VI..JASAULI</t>
+  </si>
+  <si>
+    <t>PRA.VI. KOTARABAHADURAGAMJ</t>
+  </si>
+  <si>
+    <t>PRA.VI.. KOTARABAHADURAGAMJ</t>
+  </si>
+  <si>
+    <t>PAMCHA.GHAR KOTARABAHADURAGAMJ</t>
+  </si>
+  <si>
+    <t>PAMCHA.GHAR KOTARABAHADURAGAMJ ROOM NO. 338</t>
+  </si>
+  <si>
+    <t>PAMCHA.GHAR KOTARABAHADURAGAMJ ROOM ROOM NO. 339</t>
+  </si>
+  <si>
+    <t>PAMCHA.GHAR KOTARABAHADURAGAMJ ROOM ROOM ROOM NO. 340</t>
+  </si>
+  <si>
+    <t>PAMCHA.GHAR KOTARABAHADURAGAMJ ROOM ROOM ROOM ROOM NO. 341</t>
+  </si>
+  <si>
+    <t>PAMCHA.GHAR KOTARABAHADURAGAMJ ROOM ROOM ROOM ROOM ROOM NO. 342</t>
   </si>
   <si>
     <t>praa0vi0 jmuniyaahaar kkss sN0 01</t>
@@ -763,94 +967,148 @@
     <t>praa0vi0 jmuniyaahaar kkss sN0 02</t>
   </si>
   <si>
-    <t>##0#0##0 ########### ##01</t>
-  </si>
-  <si>
-    <t>##0#0##0 ####### #### ##02</t>
-  </si>
-  <si>
-    <t>##0#0##0 ####### #### ##03</t>
-  </si>
-  <si>
-    <t>##0#0##0 ####### #### ##04</t>
-  </si>
-  <si>
-    <t>####0##0####### #### ##0 4</t>
-  </si>
-  <si>
-    <t>##0##0#######;#### ## ### #### ##0 1</t>
-  </si>
-  <si>
-    <t>##0 ##0#######;#### ## ### #### ##0 2</t>
-  </si>
-  <si>
-    <t>##0 ##0#######;#### ## ###, #### ##0 3</t>
-  </si>
-  <si>
-    <t>##0 ##0#######;#### ## ### #### ##0 4</t>
-  </si>
-  <si>
-    <t>####0##0########## ##03</t>
-  </si>
-  <si>
-    <t>####0##0####### ####, ######### ##01</t>
-  </si>
-  <si>
-    <t>####0##0####### ####, ######### ##02</t>
-  </si>
-  <si>
-    <t>##0## #####</t>
-  </si>
-  <si>
-    <t>##0 ##0 ####### #### ##01</t>
-  </si>
-  <si>
-    <t>##0 ##0 ####### #### ##02</t>
-  </si>
-  <si>
-    <t>####0##0############## ##01</t>
-  </si>
-  <si>
-    <t>####0##0#### #######, #######</t>
-  </si>
-  <si>
-    <t>####0##0######## ######### ##01</t>
-  </si>
-  <si>
-    <t>####0##0######## ######### ##02</t>
-  </si>
-  <si>
-    <t>####0##0######## ######### ##03</t>
-  </si>
-  <si>
-    <t>##0 ## ######## #####</t>
-  </si>
-  <si>
-    <t>###### ###;##0## ###### ### ######## #####</t>
-  </si>
-  <si>
-    <t>####0##0#### #### ##03</t>
-  </si>
-  <si>
-    <t>####0##0#### #### ##04</t>
-  </si>
-  <si>
-    <t>##### ##0 ######## ##01</t>
-  </si>
-  <si>
-    <t>##### ##0 ######## ##02</t>
-  </si>
-  <si>
-    <t>####0##0##### ############# ##01</t>
-  </si>
-  <si>
-    <t>####0##0##### ############# ##02</t>
-  </si>
-  <si>
-    <t>####0##0##### ############# ##03</t>
-  </si>
-  <si>
-    <t>####0 ## ########### ###</t>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM NO. 345</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM NO. 346</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM NO. 347</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM NO. 348</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM NO. 349</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM NO. 350</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 351</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 352</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 353</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 354</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 355</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 356</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 357</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 358</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 359</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 360</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 361</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 362</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 363</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 364</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 365</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 366</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 367</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 368</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 369</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 370</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 371</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 372</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 373</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 374</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 375</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 376</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 377</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 378</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 379</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 380</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 381</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 382</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 383</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 384</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 385</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 386</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 387</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 388</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 389</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 390</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 391</t>
+  </si>
+  <si>
+    <t>praa0vi0 jmuniyaahaar kkss sN0 02 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 392</t>
   </si>
   <si>
     <t>TOTAL ELECTORS</t>
@@ -932,8 +1190,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -949,7 +1215,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -957,12 +1223,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1261,91 +1545,169 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:27">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:27">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>279</v>
+        <v>365</v>
       </c>
       <c r="D2" t="s">
-        <v>280</v>
+        <v>366</v>
       </c>
       <c r="E2" t="s">
-        <v>281</v>
+        <v>367</v>
       </c>
       <c r="F2" t="s">
-        <v>282</v>
+        <v>368</v>
       </c>
       <c r="G2" t="s">
-        <v>283</v>
+        <v>369</v>
       </c>
       <c r="H2" t="s">
-        <v>284</v>
+        <v>370</v>
       </c>
       <c r="I2" t="s">
-        <v>285</v>
+        <v>371</v>
       </c>
       <c r="J2" t="s">
-        <v>286</v>
+        <v>372</v>
       </c>
       <c r="K2" t="s">
-        <v>287</v>
+        <v>373</v>
       </c>
       <c r="L2" t="s">
-        <v>288</v>
+        <v>374</v>
       </c>
       <c r="M2" t="s">
-        <v>289</v>
+        <v>375</v>
       </c>
       <c r="N2" t="s">
-        <v>290</v>
+        <v>376</v>
       </c>
       <c r="O2" t="s">
-        <v>291</v>
+        <v>377</v>
       </c>
       <c r="P2" t="s">
-        <v>292</v>
+        <v>378</v>
       </c>
       <c r="Q2" t="s">
-        <v>293</v>
+        <v>379</v>
       </c>
       <c r="R2" t="s">
-        <v>294</v>
+        <v>380</v>
       </c>
       <c r="S2" t="s">
-        <v>295</v>
+        <v>381</v>
       </c>
       <c r="T2" t="s">
-        <v>296</v>
+        <v>382</v>
       </c>
       <c r="U2" t="s">
-        <v>297</v>
+        <v>383</v>
       </c>
       <c r="V2" t="s">
-        <v>298</v>
+        <v>384</v>
       </c>
       <c r="W2" t="s">
-        <v>299</v>
+        <v>385</v>
       </c>
       <c r="X2" t="s">
-        <v>300</v>
+        <v>386</v>
       </c>
       <c r="Y2" t="s">
-        <v>301</v>
+        <v>387</v>
       </c>
       <c r="Z2" t="s">
-        <v>302</v>
+        <v>388</v>
       </c>
       <c r="AA2" t="s">
-        <v>303</v>
+        <v>389</v>
       </c>
     </row>
     <row r="3" spans="1:27">
@@ -1353,7 +1715,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C3">
         <v>791</v>
@@ -1436,7 +1798,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C4">
         <v>883</v>
@@ -1519,7 +1881,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="C5">
         <v>781</v>
@@ -1602,7 +1964,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="C6">
         <v>876</v>
@@ -1685,7 +2047,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="C7">
         <v>953</v>
@@ -1768,7 +2130,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C8">
         <v>682</v>
@@ -1851,7 +2213,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="C9">
         <v>688</v>
@@ -1934,7 +2296,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C10">
         <v>621</v>
@@ -2017,7 +2379,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C11">
         <v>1044</v>
@@ -2100,7 +2462,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C12">
         <v>892</v>
@@ -2183,7 +2545,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -2266,7 +2628,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C14">
         <v>529</v>
@@ -2349,7 +2711,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="C15">
         <v>1055</v>
@@ -2432,7 +2794,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="C16">
         <v>725</v>
@@ -2515,7 +2877,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C17">
         <v>716</v>
@@ -2598,7 +2960,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C18">
         <v>1165</v>
@@ -2681,7 +3043,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="C19">
         <v>798</v>
@@ -2764,7 +3126,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="C20">
         <v>537</v>
@@ -2847,7 +3209,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="C21">
         <v>765</v>
@@ -2930,7 +3292,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="C22">
         <v>721</v>
@@ -3013,7 +3375,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C23">
         <v>724</v>
@@ -3096,7 +3458,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="C24">
         <v>1120</v>
@@ -3179,7 +3541,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="C25">
         <v>448</v>
@@ -3262,7 +3624,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="C26">
         <v>1129</v>
@@ -3345,7 +3707,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="C27">
         <v>1088</v>
@@ -3428,7 +3790,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C28">
         <v>712</v>
@@ -3511,7 +3873,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C29">
         <v>897</v>
@@ -3594,7 +3956,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="C30">
         <v>1135</v>
@@ -3677,7 +4039,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="C31">
         <v>1139</v>
@@ -3760,7 +4122,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="C32">
         <v>864</v>
@@ -3843,7 +4205,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="C33">
         <v>469</v>
@@ -3926,7 +4288,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="C34">
         <v>582</v>
@@ -4009,7 +4371,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C35">
         <v>700</v>
@@ -4092,7 +4454,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="C36">
         <v>572</v>
@@ -4175,7 +4537,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="C37">
         <v>768</v>
@@ -4258,7 +4620,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="C38">
         <v>993</v>
@@ -4341,7 +4703,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="C39">
         <v>767</v>
@@ -4424,7 +4786,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="C40">
         <v>943</v>
@@ -4507,7 +4869,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="C41">
         <v>813</v>
@@ -4590,7 +4952,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="C42">
         <v>736</v>
@@ -4673,7 +5035,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="C43">
         <v>747</v>
@@ -4756,7 +5118,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="C44">
         <v>989</v>
@@ -4839,7 +5201,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="C45">
         <v>700</v>
@@ -4922,7 +5284,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="C46">
         <v>1128</v>
@@ -5005,7 +5367,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="C47">
         <v>1096</v>
@@ -5088,7 +5450,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="C48">
         <v>495</v>
@@ -5171,7 +5533,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="C49">
         <v>497</v>
@@ -5254,7 +5616,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="C50">
         <v>946</v>
@@ -5337,7 +5699,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="C51">
         <v>871</v>
@@ -5420,7 +5782,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="C52">
         <v>911</v>
@@ -5503,7 +5865,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="C53">
         <v>777</v>
@@ -5586,7 +5948,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="C54">
         <v>883</v>
@@ -5669,7 +6031,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="C55">
         <v>645</v>
@@ -5752,7 +6114,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="C56">
         <v>979</v>
@@ -5835,7 +6197,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="C57">
         <v>706</v>
@@ -5918,7 +6280,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="C58">
         <v>868</v>
@@ -6001,7 +6363,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="C59">
         <v>1123</v>
@@ -6084,7 +6446,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="C60">
         <v>832</v>
@@ -6167,7 +6529,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="C61">
         <v>522</v>
@@ -6250,7 +6612,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="C62">
         <v>1104</v>
@@ -6333,7 +6695,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="C63">
         <v>517</v>
@@ -6416,7 +6778,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="C64">
         <v>520</v>
@@ -6499,7 +6861,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="C65">
         <v>817</v>
@@ -6582,7 +6944,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="C66">
         <v>889</v>
@@ -6665,7 +7027,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="C67">
         <v>911</v>
@@ -6748,7 +7110,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C68">
         <v>614</v>
@@ -6831,7 +7193,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="C69">
         <v>1223</v>
@@ -6914,7 +7276,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="C70">
         <v>918</v>
@@ -6997,7 +7359,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="C71">
         <v>490</v>
@@ -7080,7 +7442,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="C72">
         <v>862</v>
@@ -7163,7 +7525,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="C73">
         <v>839</v>
@@ -7246,7 +7608,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="C74">
         <v>629</v>
@@ -7329,7 +7691,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="C75">
         <v>577</v>
@@ -7412,7 +7774,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
       <c r="C76">
         <v>592</v>
@@ -7495,7 +7857,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="C77">
         <v>784</v>
@@ -7578,7 +7940,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="C78">
         <v>561</v>
@@ -7661,7 +8023,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>11</v>
+        <v>93</v>
       </c>
       <c r="C79">
         <v>543</v>
@@ -7744,7 +8106,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>12</v>
+        <v>94</v>
       </c>
       <c r="C80">
         <v>712</v>
@@ -7827,7 +8189,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C81">
         <v>649</v>
@@ -7910,7 +8272,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="C82">
         <v>638</v>
@@ -7993,7 +8355,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="C83">
         <v>723</v>
@@ -8076,7 +8438,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="C84">
         <v>1005</v>
@@ -8159,7 +8521,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="C85">
         <v>1216</v>
@@ -8242,7 +8604,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="C86">
         <v>611</v>
@@ -8325,7 +8687,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="C87">
         <v>502</v>
@@ -8408,7 +8770,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>52</v>
+        <v>101</v>
       </c>
       <c r="C88">
         <v>1108</v>
@@ -8491,7 +8853,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="C89">
         <v>1063</v>
@@ -8574,7 +8936,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>19</v>
+        <v>103</v>
       </c>
       <c r="C90">
         <v>1055</v>
@@ -8657,7 +9019,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="C91">
         <v>1092</v>
@@ -8740,7 +9102,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="C92">
         <v>780</v>
@@ -8823,7 +9185,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>25</v>
+        <v>106</v>
       </c>
       <c r="C93">
         <v>771</v>
@@ -8906,7 +9268,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="C94">
         <v>657</v>
@@ -8989,7 +9351,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="C95">
         <v>1118</v>
@@ -9072,7 +9434,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="C96">
         <v>1121</v>
@@ -9155,7 +9517,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>69</v>
+        <v>109</v>
       </c>
       <c r="C97">
         <v>1167</v>
@@ -9238,7 +9600,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="C98">
         <v>697</v>
@@ -9321,7 +9683,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="C99">
         <v>1031</v>
@@ -9404,7 +9766,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="C100">
         <v>825</v>
@@ -9487,7 +9849,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>73</v>
+        <v>112</v>
       </c>
       <c r="C101">
         <v>733</v>
@@ -9570,7 +9932,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>32</v>
+        <v>113</v>
       </c>
       <c r="C102">
         <v>618</v>
@@ -9653,7 +10015,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>3</v>
+        <v>114</v>
       </c>
       <c r="C103">
         <v>810</v>
@@ -9736,7 +10098,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>74</v>
+        <v>115</v>
       </c>
       <c r="C104">
         <v>707</v>
@@ -9819,7 +10181,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="C105">
         <v>623</v>
@@ -9902,7 +10264,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>76</v>
+        <v>116</v>
       </c>
       <c r="C106">
         <v>456</v>
@@ -9985,7 +10347,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="C107">
         <v>1009</v>
@@ -10068,7 +10430,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="C108">
         <v>1042</v>
@@ -10151,7 +10513,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>19</v>
+        <v>118</v>
       </c>
       <c r="C109">
         <v>763</v>
@@ -10234,7 +10596,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="C110">
         <v>655</v>
@@ -10317,7 +10679,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>8</v>
+        <v>119</v>
       </c>
       <c r="C111">
         <v>1011</v>
@@ -10400,7 +10762,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="C112">
         <v>794</v>
@@ -10483,7 +10845,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="C113">
         <v>586</v>
@@ -10566,7 +10928,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="C114">
         <v>757</v>
@@ -10649,7 +11011,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="C115">
         <v>674</v>
@@ -10732,7 +11094,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="C116">
         <v>978</v>
@@ -10815,7 +11177,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="C117">
         <v>938</v>
@@ -10898,7 +11260,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="C118">
         <v>1079</v>
@@ -10981,7 +11343,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>23</v>
+        <v>126</v>
       </c>
       <c r="C119">
         <v>789</v>
@@ -11064,7 +11426,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>79</v>
+        <v>127</v>
       </c>
       <c r="C120">
         <v>1172</v>
@@ -11147,7 +11509,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="C121">
         <v>1182</v>
@@ -11230,7 +11592,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="C122">
         <v>753</v>
@@ -11313,7 +11675,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="C123">
         <v>616</v>
@@ -11396,7 +11758,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>56</v>
+        <v>131</v>
       </c>
       <c r="C124">
         <v>953</v>
@@ -11479,7 +11841,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>57</v>
+        <v>132</v>
       </c>
       <c r="C125">
         <v>430</v>
@@ -11562,7 +11924,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>23</v>
+        <v>133</v>
       </c>
       <c r="C126">
         <v>915</v>
@@ -11645,7 +12007,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="C127">
         <v>1221</v>
@@ -11728,7 +12090,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>87</v>
+        <v>135</v>
       </c>
       <c r="C128">
         <v>856</v>
@@ -11811,7 +12173,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>11</v>
+        <v>136</v>
       </c>
       <c r="C129">
         <v>1185</v>
@@ -11894,7 +12256,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>12</v>
+        <v>137</v>
       </c>
       <c r="C130">
         <v>663</v>
@@ -11977,7 +12339,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>3</v>
+        <v>137</v>
       </c>
       <c r="C131">
         <v>413</v>
@@ -12060,7 +12422,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>88</v>
+        <v>138</v>
       </c>
       <c r="C132">
         <v>686</v>
@@ -12143,7 +12505,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>89</v>
+        <v>139</v>
       </c>
       <c r="C133">
         <v>618</v>
@@ -12226,7 +12588,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="C134">
         <v>611</v>
@@ -12309,7 +12671,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>91</v>
+        <v>141</v>
       </c>
       <c r="C135">
         <v>1189</v>
@@ -12392,7 +12754,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>92</v>
+        <v>142</v>
       </c>
       <c r="C136">
         <v>822</v>
@@ -12475,7 +12837,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="C137">
         <v>1063</v>
@@ -12558,7 +12920,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>94</v>
+        <v>144</v>
       </c>
       <c r="C138">
         <v>633</v>
@@ -12641,7 +13003,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="C139">
         <v>973</v>
@@ -12724,7 +13086,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>96</v>
+        <v>145</v>
       </c>
       <c r="C140">
         <v>980</v>
@@ -12807,7 +13169,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>97</v>
+        <v>146</v>
       </c>
       <c r="C141">
         <v>863</v>
@@ -12890,7 +13252,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>98</v>
+        <v>147</v>
       </c>
       <c r="C142">
         <v>1015</v>
@@ -12973,7 +13335,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>99</v>
+        <v>148</v>
       </c>
       <c r="C143">
         <v>864</v>
@@ -13056,7 +13418,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>100</v>
+        <v>149</v>
       </c>
       <c r="C144">
         <v>1228</v>
@@ -13139,7 +13501,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>101</v>
+        <v>150</v>
       </c>
       <c r="C145">
         <v>865</v>
@@ -13222,7 +13584,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>102</v>
+        <v>151</v>
       </c>
       <c r="C146">
         <v>1058</v>
@@ -13305,7 +13667,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>103</v>
+        <v>152</v>
       </c>
       <c r="C147">
         <v>1090</v>
@@ -13388,7 +13750,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>99</v>
+        <v>152</v>
       </c>
       <c r="C148">
         <v>532</v>
@@ -13471,7 +13833,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>104</v>
+        <v>153</v>
       </c>
       <c r="C149">
         <v>1035</v>
@@ -13554,7 +13916,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="C150">
         <v>1067</v>
@@ -13637,7 +13999,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>106</v>
+        <v>155</v>
       </c>
       <c r="C151">
         <v>552</v>
@@ -13720,7 +14082,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>107</v>
+        <v>156</v>
       </c>
       <c r="C152">
         <v>719</v>
@@ -13803,7 +14165,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>108</v>
+        <v>157</v>
       </c>
       <c r="C153">
         <v>739</v>
@@ -13886,7 +14248,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>109</v>
+        <v>158</v>
       </c>
       <c r="C154">
         <v>646</v>
@@ -13969,7 +14331,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>110</v>
+        <v>158</v>
       </c>
       <c r="C155">
         <v>657</v>
@@ -14052,7 +14414,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>99</v>
+        <v>159</v>
       </c>
       <c r="C156">
         <v>841</v>
@@ -14135,7 +14497,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>111</v>
+        <v>160</v>
       </c>
       <c r="C157">
         <v>826</v>
@@ -14218,7 +14580,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>112</v>
+        <v>160</v>
       </c>
       <c r="C158">
         <v>898</v>
@@ -14301,7 +14663,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>113</v>
+        <v>161</v>
       </c>
       <c r="C159">
         <v>735</v>
@@ -14384,7 +14746,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>114</v>
+        <v>162</v>
       </c>
       <c r="C160">
         <v>697</v>
@@ -14467,7 +14829,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="C161">
         <v>1006</v>
@@ -14550,7 +14912,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>116</v>
+        <v>163</v>
       </c>
       <c r="C162">
         <v>825</v>
@@ -14633,7 +14995,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>117</v>
+        <v>164</v>
       </c>
       <c r="C163">
         <v>573</v>
@@ -14716,7 +15078,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="C164">
         <v>513</v>
@@ -14799,7 +15161,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>119</v>
+        <v>165</v>
       </c>
       <c r="C165">
         <v>817</v>
@@ -14882,7 +15244,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>120</v>
+        <v>166</v>
       </c>
       <c r="C166">
         <v>735</v>
@@ -14965,7 +15327,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>121</v>
+        <v>167</v>
       </c>
       <c r="C167">
         <v>1152</v>
@@ -15048,7 +15410,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>122</v>
+        <v>168</v>
       </c>
       <c r="C168">
         <v>648</v>
@@ -15131,7 +15493,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>123</v>
+        <v>169</v>
       </c>
       <c r="C169">
         <v>1229</v>
@@ -15214,7 +15576,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>124</v>
+        <v>170</v>
       </c>
       <c r="C170">
         <v>1109</v>
@@ -15297,7 +15659,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>125</v>
+        <v>171</v>
       </c>
       <c r="C171">
         <v>1218</v>
@@ -15380,7 +15742,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>126</v>
+        <v>170</v>
       </c>
       <c r="C172">
         <v>951</v>
@@ -15463,7 +15825,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="C173">
         <v>741</v>
@@ -15546,7 +15908,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="C174">
         <v>691</v>
@@ -15629,7 +15991,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="C175">
         <v>1051</v>
@@ -15712,7 +16074,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="C176">
         <v>1201</v>
@@ -15795,7 +16157,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>112</v>
+        <v>176</v>
       </c>
       <c r="C177">
         <v>959</v>
@@ -15878,7 +16240,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="C178">
         <v>954</v>
@@ -15961,7 +16323,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="C179">
         <v>1095</v>
@@ -16044,7 +16406,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="C180">
         <v>879</v>
@@ -16127,7 +16489,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="C181">
         <v>1141</v>
@@ -16210,7 +16572,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="C182">
         <v>1088</v>
@@ -16293,7 +16655,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
       <c r="C183">
         <v>1111</v>
@@ -16376,7 +16738,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>105</v>
+        <v>182</v>
       </c>
       <c r="C184">
         <v>1174</v>
@@ -16459,7 +16821,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>106</v>
+        <v>183</v>
       </c>
       <c r="C185">
         <v>426</v>
@@ -16542,7 +16904,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>137</v>
+        <v>184</v>
       </c>
       <c r="C186">
         <v>750</v>
@@ -16625,7 +16987,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>138</v>
+        <v>184</v>
       </c>
       <c r="C187">
         <v>732</v>
@@ -16708,7 +17070,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>134</v>
+        <v>185</v>
       </c>
       <c r="C188">
         <v>1061</v>
@@ -16791,7 +17153,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>135</v>
+        <v>186</v>
       </c>
       <c r="C189">
         <v>585</v>
@@ -16874,7 +17236,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>139</v>
+        <v>187</v>
       </c>
       <c r="C190">
         <v>937</v>
@@ -16957,7 +17319,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="C191">
         <v>909</v>
@@ -17040,7 +17402,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>141</v>
+        <v>189</v>
       </c>
       <c r="C192">
         <v>1210</v>
@@ -17123,7 +17485,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>142</v>
+        <v>190</v>
       </c>
       <c r="C193">
         <v>869</v>
@@ -17206,7 +17568,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>143</v>
+        <v>190</v>
       </c>
       <c r="C194">
         <v>1072</v>
@@ -17289,7 +17651,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="C195">
         <v>1168</v>
@@ -17372,7 +17734,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="C196">
         <v>1143</v>
@@ -17455,7 +17817,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>146</v>
+        <v>193</v>
       </c>
       <c r="C197">
         <v>1176</v>
@@ -17538,7 +17900,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>147</v>
+        <v>194</v>
       </c>
       <c r="C198">
         <v>809</v>
@@ -17621,7 +17983,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>148</v>
+        <v>194</v>
       </c>
       <c r="C199">
         <v>666</v>
@@ -17704,7 +18066,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>149</v>
+        <v>195</v>
       </c>
       <c r="C200">
         <v>1173</v>
@@ -17787,7 +18149,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>150</v>
+        <v>196</v>
       </c>
       <c r="C201">
         <v>963</v>
@@ -17870,7 +18232,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>151</v>
+        <v>197</v>
       </c>
       <c r="C202">
         <v>874</v>
@@ -17953,7 +18315,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>152</v>
+        <v>197</v>
       </c>
       <c r="C203">
         <v>1015</v>
@@ -18036,7 +18398,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>153</v>
+        <v>198</v>
       </c>
       <c r="C204">
         <v>1144</v>
@@ -18119,7 +18481,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>154</v>
+        <v>199</v>
       </c>
       <c r="C205">
         <v>817</v>
@@ -18202,7 +18564,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>155</v>
+        <v>199</v>
       </c>
       <c r="C206">
         <v>505</v>
@@ -18285,7 +18647,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>105</v>
+        <v>200</v>
       </c>
       <c r="C207">
         <v>880</v>
@@ -18368,7 +18730,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>106</v>
+        <v>201</v>
       </c>
       <c r="C208">
         <v>687</v>
@@ -18451,7 +18813,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>156</v>
+        <v>202</v>
       </c>
       <c r="C209">
         <v>607</v>
@@ -18534,7 +18896,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>157</v>
+        <v>203</v>
       </c>
       <c r="C210">
         <v>918</v>
@@ -18617,7 +18979,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>158</v>
+        <v>204</v>
       </c>
       <c r="C211">
         <v>881</v>
@@ -18700,7 +19062,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>159</v>
+        <v>205</v>
       </c>
       <c r="C212">
         <v>876</v>
@@ -18783,7 +19145,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>160</v>
+        <v>206</v>
       </c>
       <c r="C213">
         <v>963</v>
@@ -18866,7 +19228,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>161</v>
+        <v>207</v>
       </c>
       <c r="C214">
         <v>883</v>
@@ -18949,7 +19311,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>162</v>
+        <v>208</v>
       </c>
       <c r="C215">
         <v>922</v>
@@ -19032,7 +19394,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>163</v>
+        <v>209</v>
       </c>
       <c r="C216">
         <v>1250</v>
@@ -19115,7 +19477,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>164</v>
+        <v>210</v>
       </c>
       <c r="C217">
         <v>944</v>
@@ -19198,7 +19560,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>165</v>
+        <v>211</v>
       </c>
       <c r="C218">
         <v>1140</v>
@@ -19281,7 +19643,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>166</v>
+        <v>212</v>
       </c>
       <c r="C219">
         <v>821</v>
@@ -19364,7 +19726,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>134</v>
+        <v>213</v>
       </c>
       <c r="C220">
         <v>750</v>
@@ -19447,7 +19809,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>135</v>
+        <v>214</v>
       </c>
       <c r="C221">
         <v>621</v>
@@ -19530,7 +19892,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>167</v>
+        <v>215</v>
       </c>
       <c r="C222">
         <v>745</v>
@@ -19613,7 +19975,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>168</v>
+        <v>216</v>
       </c>
       <c r="C223">
         <v>1039</v>
@@ -19696,7 +20058,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>121</v>
+        <v>216</v>
       </c>
       <c r="C224">
         <v>1101</v>
@@ -19779,7 +20141,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>122</v>
+        <v>217</v>
       </c>
       <c r="C225">
         <v>1043</v>
@@ -19862,7 +20224,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>137</v>
+        <v>218</v>
       </c>
       <c r="C226">
         <v>1208</v>
@@ -19945,7 +20307,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>169</v>
+        <v>219</v>
       </c>
       <c r="C227">
         <v>977</v>
@@ -20028,7 +20390,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>149</v>
+        <v>220</v>
       </c>
       <c r="C228">
         <v>716</v>
@@ -20111,7 +20473,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>150</v>
+        <v>221</v>
       </c>
       <c r="C229">
         <v>707</v>
@@ -20194,7 +20556,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>170</v>
+        <v>222</v>
       </c>
       <c r="C230">
         <v>665</v>
@@ -20277,7 +20639,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>171</v>
+        <v>222</v>
       </c>
       <c r="C231">
         <v>679</v>
@@ -20360,7 +20722,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>172</v>
+        <v>223</v>
       </c>
       <c r="C232">
         <v>809</v>
@@ -20443,7 +20805,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>173</v>
+        <v>224</v>
       </c>
       <c r="C233">
         <v>1095</v>
@@ -20526,7 +20888,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>174</v>
+        <v>225</v>
       </c>
       <c r="C234">
         <v>1196</v>
@@ -20609,7 +20971,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>175</v>
+        <v>225</v>
       </c>
       <c r="C235">
         <v>1102</v>
@@ -20692,7 +21054,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>176</v>
+        <v>226</v>
       </c>
       <c r="C236">
         <v>1082</v>
@@ -20775,7 +21137,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>177</v>
+        <v>227</v>
       </c>
       <c r="C237">
         <v>796</v>
@@ -20858,7 +21220,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>178</v>
+        <v>228</v>
       </c>
       <c r="C238">
         <v>738</v>
@@ -20941,7 +21303,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>179</v>
+        <v>229</v>
       </c>
       <c r="C239">
         <v>711</v>
@@ -21024,7 +21386,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>180</v>
+        <v>230</v>
       </c>
       <c r="C240">
         <v>715</v>
@@ -21107,7 +21469,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>181</v>
+        <v>231</v>
       </c>
       <c r="C241">
         <v>735</v>
@@ -21190,7 +21552,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>182</v>
+        <v>232</v>
       </c>
       <c r="C242">
         <v>717</v>
@@ -21273,7 +21635,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>183</v>
+        <v>233</v>
       </c>
       <c r="C243">
         <v>686</v>
@@ -21356,7 +21718,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>184</v>
+        <v>234</v>
       </c>
       <c r="C244">
         <v>839</v>
@@ -21439,7 +21801,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>149</v>
+        <v>235</v>
       </c>
       <c r="C245">
         <v>718</v>
@@ -21522,7 +21884,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>150</v>
+        <v>235</v>
       </c>
       <c r="C246">
         <v>703</v>
@@ -21605,7 +21967,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>101</v>
+        <v>236</v>
       </c>
       <c r="C247">
         <v>942</v>
@@ -21688,7 +22050,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>102</v>
+        <v>237</v>
       </c>
       <c r="C248">
         <v>1039</v>
@@ -21771,7 +22133,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>133</v>
+        <v>237</v>
       </c>
       <c r="C249">
         <v>508</v>
@@ -21854,7 +22216,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>137</v>
+        <v>238</v>
       </c>
       <c r="C250">
         <v>732</v>
@@ -21937,7 +22299,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>133</v>
+        <v>239</v>
       </c>
       <c r="C251">
         <v>842</v>
@@ -22020,7 +22382,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>185</v>
+        <v>240</v>
       </c>
       <c r="C252">
         <v>451</v>
@@ -22103,7 +22465,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>186</v>
+        <v>241</v>
       </c>
       <c r="C253">
         <v>872</v>
@@ -22186,7 +22548,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>187</v>
+        <v>241</v>
       </c>
       <c r="C254">
         <v>881</v>
@@ -22269,7 +22631,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>188</v>
+        <v>242</v>
       </c>
       <c r="C255">
         <v>907</v>
@@ -22352,7 +22714,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>189</v>
+        <v>243</v>
       </c>
       <c r="C256">
         <v>1137</v>
@@ -22435,7 +22797,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>190</v>
+        <v>244</v>
       </c>
       <c r="C257">
         <v>648</v>
@@ -22518,7 +22880,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>191</v>
+        <v>245</v>
       </c>
       <c r="C258">
         <v>939</v>
@@ -22601,7 +22963,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>192</v>
+        <v>246</v>
       </c>
       <c r="C259">
         <v>735</v>
@@ -22684,7 +23046,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>193</v>
+        <v>247</v>
       </c>
       <c r="C260">
         <v>870</v>
@@ -22767,7 +23129,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>134</v>
+        <v>248</v>
       </c>
       <c r="C261">
         <v>982</v>
@@ -22850,7 +23212,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>135</v>
+        <v>249</v>
       </c>
       <c r="C262">
         <v>1160</v>
@@ -22933,7 +23295,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>194</v>
+        <v>250</v>
       </c>
       <c r="C263">
         <v>1197</v>
@@ -23016,7 +23378,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>195</v>
+        <v>251</v>
       </c>
       <c r="C264">
         <v>290</v>
@@ -23099,7 +23461,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>196</v>
+        <v>251</v>
       </c>
       <c r="C265">
         <v>797</v>
@@ -23182,7 +23544,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>197</v>
+        <v>252</v>
       </c>
       <c r="C266">
         <v>1090</v>
@@ -23265,7 +23627,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>198</v>
+        <v>253</v>
       </c>
       <c r="C267">
         <v>1018</v>
@@ -23348,7 +23710,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>199</v>
+        <v>254</v>
       </c>
       <c r="C268">
         <v>954</v>
@@ -23431,7 +23793,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>137</v>
+        <v>255</v>
       </c>
       <c r="C269">
         <v>976</v>
@@ -23514,7 +23876,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>200</v>
+        <v>255</v>
       </c>
       <c r="C270">
         <v>668</v>
@@ -23597,7 +23959,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>201</v>
+        <v>256</v>
       </c>
       <c r="C271">
         <v>656</v>
@@ -23680,7 +24042,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>202</v>
+        <v>257</v>
       </c>
       <c r="C272">
         <v>1027</v>
@@ -23763,7 +24125,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>115</v>
+        <v>258</v>
       </c>
       <c r="C273">
         <v>1085</v>
@@ -23846,7 +24208,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>203</v>
+        <v>259</v>
       </c>
       <c r="C274">
         <v>799</v>
@@ -23929,7 +24291,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>204</v>
+        <v>260</v>
       </c>
       <c r="C275">
         <v>716</v>
@@ -24012,7 +24374,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>138</v>
+        <v>261</v>
       </c>
       <c r="C276">
         <v>1103</v>
@@ -24095,7 +24457,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>112</v>
+        <v>262</v>
       </c>
       <c r="C277">
         <v>748</v>
@@ -24178,7 +24540,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>113</v>
+        <v>263</v>
       </c>
       <c r="C278">
         <v>754</v>
@@ -24261,7 +24623,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>205</v>
+        <v>264</v>
       </c>
       <c r="C279">
         <v>731</v>
@@ -24344,7 +24706,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>137</v>
+        <v>265</v>
       </c>
       <c r="C280">
         <v>800</v>
@@ -24427,7 +24789,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>206</v>
+        <v>266</v>
       </c>
       <c r="C281">
         <v>793</v>
@@ -24510,7 +24872,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>207</v>
+        <v>267</v>
       </c>
       <c r="C282">
         <v>846</v>
@@ -24593,7 +24955,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>208</v>
+        <v>268</v>
       </c>
       <c r="C283">
         <v>555</v>
@@ -24676,7 +25038,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>105</v>
+        <v>269</v>
       </c>
       <c r="C284">
         <v>848</v>
@@ -24759,7 +25121,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>106</v>
+        <v>270</v>
       </c>
       <c r="C285">
         <v>980</v>
@@ -24842,7 +25204,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>209</v>
+        <v>271</v>
       </c>
       <c r="C286">
         <v>795</v>
@@ -24925,7 +25287,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>210</v>
+        <v>271</v>
       </c>
       <c r="C287">
         <v>698</v>
@@ -25008,7 +25370,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>211</v>
+        <v>272</v>
       </c>
       <c r="C288">
         <v>913</v>
@@ -25091,7 +25453,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>212</v>
+        <v>273</v>
       </c>
       <c r="C289">
         <v>518</v>
@@ -25174,7 +25536,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>213</v>
+        <v>273</v>
       </c>
       <c r="C290">
         <v>616</v>
@@ -25257,7 +25619,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>214</v>
+        <v>274</v>
       </c>
       <c r="C291">
         <v>736</v>
@@ -25340,7 +25702,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>215</v>
+        <v>274</v>
       </c>
       <c r="C292">
         <v>1163</v>
@@ -25423,7 +25785,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>216</v>
+        <v>275</v>
       </c>
       <c r="C293">
         <v>771</v>
@@ -25506,7 +25868,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>217</v>
+        <v>276</v>
       </c>
       <c r="C294">
         <v>943</v>
@@ -25589,7 +25951,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>218</v>
+        <v>277</v>
       </c>
       <c r="C295">
         <v>745</v>
@@ -25672,7 +26034,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>219</v>
+        <v>277</v>
       </c>
       <c r="C296">
         <v>992</v>
@@ -25755,7 +26117,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>220</v>
+        <v>278</v>
       </c>
       <c r="C297">
         <v>951</v>
@@ -25838,7 +26200,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>219</v>
+        <v>279</v>
       </c>
       <c r="C298">
         <v>893</v>
@@ -25921,7 +26283,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>221</v>
+        <v>279</v>
       </c>
       <c r="C299">
         <v>977</v>
@@ -26004,7 +26366,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>222</v>
+        <v>279</v>
       </c>
       <c r="C300">
         <v>872</v>
@@ -26087,7 +26449,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>104</v>
+        <v>279</v>
       </c>
       <c r="C301">
         <v>1058</v>
@@ -26170,7 +26532,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>223</v>
+        <v>280</v>
       </c>
       <c r="C302">
         <v>662</v>
@@ -26253,7 +26615,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>175</v>
+        <v>280</v>
       </c>
       <c r="C303">
         <v>817</v>
@@ -26336,7 +26698,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>176</v>
+        <v>281</v>
       </c>
       <c r="C304">
         <v>783</v>
@@ -26419,7 +26781,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>224</v>
+        <v>282</v>
       </c>
       <c r="C305">
         <v>595</v>
@@ -26502,7 +26864,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>225</v>
+        <v>282</v>
       </c>
       <c r="C306">
         <v>1069</v>
@@ -26585,7 +26947,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>124</v>
+        <v>282</v>
       </c>
       <c r="C307">
         <v>906</v>
@@ -26668,7 +27030,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>226</v>
+        <v>282</v>
       </c>
       <c r="C308">
         <v>603</v>
@@ -26751,7 +27113,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>124</v>
+        <v>283</v>
       </c>
       <c r="C309">
         <v>1205</v>
@@ -26834,7 +27196,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>173</v>
+        <v>284</v>
       </c>
       <c r="C310">
         <v>934</v>
@@ -26917,7 +27279,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>174</v>
+        <v>284</v>
       </c>
       <c r="C311">
         <v>1058</v>
@@ -27000,7 +27362,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>215</v>
+        <v>285</v>
       </c>
       <c r="C312">
         <v>523</v>
@@ -27083,7 +27445,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>227</v>
+        <v>286</v>
       </c>
       <c r="C313">
         <v>445</v>
@@ -27166,7 +27528,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>228</v>
+        <v>287</v>
       </c>
       <c r="C314">
         <v>499</v>
@@ -27249,7 +27611,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>209</v>
+        <v>288</v>
       </c>
       <c r="C315">
         <v>690</v>
@@ -27332,7 +27694,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>210</v>
+        <v>289</v>
       </c>
       <c r="C316">
         <v>738</v>
@@ -27415,7 +27777,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>229</v>
+        <v>290</v>
       </c>
       <c r="C317">
         <v>517</v>
@@ -27498,7 +27860,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>173</v>
+        <v>291</v>
       </c>
       <c r="C318">
         <v>760</v>
@@ -27581,7 +27943,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>174</v>
+        <v>292</v>
       </c>
       <c r="C319">
         <v>740</v>
@@ -27664,7 +28026,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>123</v>
+        <v>293</v>
       </c>
       <c r="C320">
         <v>1055</v>
@@ -27747,7 +28109,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>119</v>
+        <v>294</v>
       </c>
       <c r="C321">
         <v>1088</v>
@@ -27830,7 +28192,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>230</v>
+        <v>295</v>
       </c>
       <c r="C322">
         <v>741</v>
@@ -27913,7 +28275,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>99</v>
+        <v>296</v>
       </c>
       <c r="C323">
         <v>1169</v>
@@ -27996,7 +28358,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>231</v>
+        <v>296</v>
       </c>
       <c r="C324">
         <v>666</v>
@@ -28079,7 +28441,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>232</v>
+        <v>297</v>
       </c>
       <c r="C325">
         <v>781</v>
@@ -28162,7 +28524,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>233</v>
+        <v>298</v>
       </c>
       <c r="C326">
         <v>899</v>
@@ -28245,7 +28607,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>234</v>
+        <v>299</v>
       </c>
       <c r="C327">
         <v>627</v>
@@ -28328,7 +28690,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>222</v>
+        <v>300</v>
       </c>
       <c r="C328">
         <v>1015</v>
@@ -28411,7 +28773,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>235</v>
+        <v>301</v>
       </c>
       <c r="C329">
         <v>754</v>
@@ -28494,7 +28856,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>236</v>
+        <v>302</v>
       </c>
       <c r="C330">
         <v>784</v>
@@ -28577,7 +28939,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>175</v>
+        <v>303</v>
       </c>
       <c r="C331">
         <v>947</v>
@@ -28660,7 +29022,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>176</v>
+        <v>304</v>
       </c>
       <c r="C332">
         <v>917</v>
@@ -28743,7 +29105,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>237</v>
+        <v>304</v>
       </c>
       <c r="C333">
         <v>1056</v>
@@ -28826,7 +29188,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>238</v>
+        <v>305</v>
       </c>
       <c r="C334">
         <v>353</v>
@@ -28909,7 +29271,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>209</v>
+        <v>305</v>
       </c>
       <c r="C335">
         <v>748</v>
@@ -28992,7 +29354,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>106</v>
+        <v>306</v>
       </c>
       <c r="C336">
         <v>510</v>
@@ -29075,7 +29437,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>239</v>
+        <v>307</v>
       </c>
       <c r="C337">
         <v>1203</v>
@@ -29158,7 +29520,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>240</v>
+        <v>308</v>
       </c>
       <c r="C338">
         <v>572</v>
@@ -29241,7 +29603,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>241</v>
+        <v>309</v>
       </c>
       <c r="C339">
         <v>759</v>
@@ -29324,7 +29686,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>242</v>
+        <v>310</v>
       </c>
       <c r="C340">
         <v>1220</v>
@@ -29407,7 +29769,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>243</v>
+        <v>311</v>
       </c>
       <c r="C341">
         <v>1038</v>
@@ -29490,7 +29852,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>244</v>
+        <v>312</v>
       </c>
       <c r="C342">
         <v>1078</v>
@@ -29573,7 +29935,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>245</v>
+        <v>313</v>
       </c>
       <c r="C343">
         <v>415</v>
@@ -29656,7 +30018,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>246</v>
+        <v>314</v>
       </c>
       <c r="C344">
         <v>1198</v>
@@ -29739,7 +30101,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>247</v>
+        <v>315</v>
       </c>
       <c r="C345">
         <v>643</v>
@@ -29822,7 +30184,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>248</v>
+        <v>316</v>
       </c>
       <c r="C346">
         <v>595</v>
@@ -29905,7 +30267,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>249</v>
+        <v>317</v>
       </c>
       <c r="C347">
         <v>1129</v>
@@ -29988,7 +30350,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>250</v>
+        <v>318</v>
       </c>
       <c r="C348">
         <v>727</v>
@@ -30071,7 +30433,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>251</v>
+        <v>319</v>
       </c>
       <c r="C349">
         <v>906</v>
@@ -30154,7 +30516,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>252</v>
+        <v>320</v>
       </c>
       <c r="C350">
         <v>731</v>
@@ -30237,7 +30599,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>175</v>
+        <v>321</v>
       </c>
       <c r="C351">
         <v>1057</v>
@@ -30320,7 +30682,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>176</v>
+        <v>322</v>
       </c>
       <c r="C352">
         <v>1079</v>
@@ -30403,7 +30765,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>177</v>
+        <v>323</v>
       </c>
       <c r="C353">
         <v>1152</v>
@@ -30486,7 +30848,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>253</v>
+        <v>324</v>
       </c>
       <c r="C354">
         <v>996</v>
@@ -30569,7 +30931,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>254</v>
+        <v>325</v>
       </c>
       <c r="C355">
         <v>1083</v>
@@ -30652,7 +31014,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>255</v>
+        <v>326</v>
       </c>
       <c r="C356">
         <v>1159</v>
@@ -30735,7 +31097,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>256</v>
+        <v>327</v>
       </c>
       <c r="C357">
         <v>1051</v>
@@ -30818,7 +31180,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>257</v>
+        <v>328</v>
       </c>
       <c r="C358">
         <v>998</v>
@@ -30901,7 +31263,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>173</v>
+        <v>329</v>
       </c>
       <c r="C359">
         <v>971</v>
@@ -30984,7 +31346,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>174</v>
+        <v>330</v>
       </c>
       <c r="C360">
         <v>1057</v>
@@ -31067,7 +31429,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>258</v>
+        <v>331</v>
       </c>
       <c r="C361">
         <v>749</v>
@@ -31150,7 +31512,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>103</v>
+        <v>332</v>
       </c>
       <c r="C362">
         <v>776</v>
@@ -31233,7 +31595,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>99</v>
+        <v>333</v>
       </c>
       <c r="C363">
         <v>992</v>
@@ -31316,7 +31678,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>259</v>
+        <v>334</v>
       </c>
       <c r="C364">
         <v>1035</v>
@@ -31399,7 +31761,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>260</v>
+        <v>335</v>
       </c>
       <c r="C365">
         <v>1020</v>
@@ -31482,7 +31844,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>261</v>
+        <v>336</v>
       </c>
       <c r="C366">
         <v>1150</v>
@@ -31565,7 +31927,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>99</v>
+        <v>337</v>
       </c>
       <c r="C367">
         <v>1085</v>
@@ -31648,7 +32010,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>108</v>
+        <v>338</v>
       </c>
       <c r="C368">
         <v>957</v>
@@ -31731,7 +32093,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>262</v>
+        <v>339</v>
       </c>
       <c r="C369">
         <v>1154</v>
@@ -31814,7 +32176,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>263</v>
+        <v>340</v>
       </c>
       <c r="C370">
         <v>688</v>
@@ -31897,7 +32259,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>99</v>
+        <v>341</v>
       </c>
       <c r="C371">
         <v>805</v>
@@ -31980,7 +32342,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>264</v>
+        <v>342</v>
       </c>
       <c r="C372">
         <v>832</v>
@@ -32063,7 +32425,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>127</v>
+        <v>343</v>
       </c>
       <c r="C373">
         <v>807</v>
@@ -32146,7 +32508,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>265</v>
+        <v>344</v>
       </c>
       <c r="C374">
         <v>915</v>
@@ -32229,7 +32591,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>175</v>
+        <v>345</v>
       </c>
       <c r="C375">
         <v>894</v>
@@ -32312,7 +32674,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>176</v>
+        <v>346</v>
       </c>
       <c r="C376">
         <v>1076</v>
@@ -32395,7 +32757,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>134</v>
+        <v>347</v>
       </c>
       <c r="C377">
         <v>781</v>
@@ -32478,7 +32840,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>135</v>
+        <v>348</v>
       </c>
       <c r="C378">
         <v>682</v>
@@ -32561,7 +32923,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>266</v>
+        <v>349</v>
       </c>
       <c r="C379">
         <v>956</v>
@@ -32644,7 +33006,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>267</v>
+        <v>350</v>
       </c>
       <c r="C380">
         <v>1182</v>
@@ -32727,7 +33089,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>268</v>
+        <v>351</v>
       </c>
       <c r="C381">
         <v>1050</v>
@@ -32810,7 +33172,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>269</v>
+        <v>352</v>
       </c>
       <c r="C382">
         <v>1003</v>
@@ -32893,7 +33255,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>270</v>
+        <v>353</v>
       </c>
       <c r="C383">
         <v>423</v>
@@ -32976,7 +33338,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>239</v>
+        <v>354</v>
       </c>
       <c r="C384">
         <v>980</v>
@@ -33059,7 +33421,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>240</v>
+        <v>355</v>
       </c>
       <c r="C385">
         <v>1070</v>
@@ -33142,7 +33504,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>271</v>
+        <v>356</v>
       </c>
       <c r="C386">
         <v>1053</v>
@@ -33225,7 +33587,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>272</v>
+        <v>357</v>
       </c>
       <c r="C387">
         <v>1059</v>
@@ -33308,7 +33670,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>273</v>
+        <v>358</v>
       </c>
       <c r="C388">
         <v>1103</v>
@@ -33391,7 +33753,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>274</v>
+        <v>359</v>
       </c>
       <c r="C389">
         <v>1195</v>
@@ -33474,7 +33836,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>123</v>
+        <v>360</v>
       </c>
       <c r="C390">
         <v>960</v>
@@ -33557,7 +33919,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>275</v>
+        <v>361</v>
       </c>
       <c r="C391">
         <v>740</v>
@@ -33640,7 +34002,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>276</v>
+        <v>362</v>
       </c>
       <c r="C392">
         <v>920</v>
@@ -33723,7 +34085,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>277</v>
+        <v>363</v>
       </c>
       <c r="C393">
         <v>1202</v>
@@ -33806,7 +34168,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>278</v>
+        <v>364</v>
       </c>
       <c r="C394">
         <v>1106</v>
